--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.89842647499107</v>
+        <v>2.90849430218605</v>
       </c>
       <c r="D2" t="n">
-        <v>17.40097505202165</v>
+        <v>2.827658445953519</v>
       </c>
       <c r="E2" t="n">
-        <v>9.116364391642069</v>
+        <v>1.481409213641836</v>
       </c>
       <c r="F2" t="n">
-        <v>8.963674135109073</v>
+        <v>1.456597046955225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.748876831192105</v>
+        <v>1.421692485068717</v>
       </c>
       <c r="D3" t="n">
-        <v>9.496030521916929</v>
+        <v>1.543104959811501</v>
       </c>
       <c r="E3" t="n">
-        <v>9.116364391642069</v>
+        <v>1.481409213641836</v>
       </c>
       <c r="F3" t="n">
-        <v>8.963674135109073</v>
+        <v>1.456597046955225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.96453470162806</v>
+        <v>5.031736889014559</v>
       </c>
       <c r="D4" t="n">
-        <v>31.18821620020911</v>
+        <v>5.068085132533981</v>
       </c>
       <c r="E4" t="n">
-        <v>9.116364391642069</v>
+        <v>1.481409213641836</v>
       </c>
       <c r="F4" t="n">
-        <v>8.963674135109073</v>
+        <v>1.456597046955225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
